--- a/data/seed/structuur.xlsx
+++ b/data/seed/structuur.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willemjanssen/Documents/MAMP/st/data/seed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E13DCC6C-9891-5247-9BA2-21ECEA8108F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD63668-DAE8-1946-A606-592ABF1B516B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27560" yWindow="500" windowWidth="41240" windowHeight="25400" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27560" yWindow="500" windowWidth="41240" windowHeight="25400" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructies" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="798">
   <si>
     <t>Structuur-template</t>
   </si>
@@ -2425,21 +2425,6 @@
   </si>
   <si>
     <t>Heb je aanvullende opmerkingen?</t>
-  </si>
-  <si>
-    <t>De demo</t>
-  </si>
-  <si>
-    <t>Het systeem</t>
-  </si>
-  <si>
-    <t>Risico check</t>
-  </si>
-  <si>
-    <t>De leverancier</t>
-  </si>
-  <si>
-    <t>Open vragen</t>
   </si>
 </sst>
 </file>
@@ -6872,7 +6857,7 @@
   <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" style="13" customWidth="1"/>
+    <col min="1" max="1" width="10" style="13" customWidth="1"/>
     <col min="2" max="2" width="85" style="13" customWidth="1"/>
     <col min="3" max="16384" width="8.83203125" style="13"/>
   </cols>
@@ -6886,152 +6871,152 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="40" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>798</v>
+      <c r="A2" s="11">
+        <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>779</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="40" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>798</v>
+      <c r="A3" s="11">
+        <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>780</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>798</v>
+      <c r="A4" s="11">
+        <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>781</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>798</v>
+      <c r="A5" s="11">
+        <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>782</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>798</v>
+      <c r="A6" s="11">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>799</v>
+      <c r="A7" s="11">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>784</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>799</v>
+      <c r="A8" s="11">
+        <v>2</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>785</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>799</v>
+      <c r="A9" s="11">
+        <v>2</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>786</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>799</v>
+      <c r="A10" s="11">
+        <v>2</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>787</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="40" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>800</v>
+      <c r="A11" s="11">
+        <v>3</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>788</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>800</v>
+      <c r="A12" s="11">
+        <v>3</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>789</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>800</v>
+      <c r="A13" s="11">
+        <v>3</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>790</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="40" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>801</v>
+      <c r="A14" s="11">
+        <v>4</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>801</v>
+      <c r="A15" s="11">
+        <v>4</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>792</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>801</v>
+      <c r="A16" s="11">
+        <v>4</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>793</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>802</v>
+      <c r="A17" s="11">
+        <v>5</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>794</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
-        <v>802</v>
+      <c r="A18" s="11">
+        <v>5</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>795</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>802</v>
+      <c r="A19" s="11">
+        <v>5</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>796</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>802</v>
+      <c r="A20" s="11">
+        <v>5</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>797</v>
